--- a/jira_export_2026-10-14.xlsx
+++ b/jira_export_2026-10-14.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>212 h</t>
+          <t>222 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>293</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -1605,7 +1605,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>1</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>4</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>12.25</v>
+        <v>15.5</v>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>576</v>
       </c>
       <c r="P49" s="12" t="n">
-        <v>47.02</v>
+        <v>37.16</v>
       </c>
     </row>
     <row r="50">
@@ -4885,7 +4885,7 @@
         <v>4</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>2.25</v>
+        <v>4.25</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>308</v>
       </c>
       <c r="P58" s="15" t="n">
-        <v>136.89</v>
+        <v>72.47</v>
       </c>
     </row>
     <row r="59">
@@ -9329,7 +9329,7 @@
         <v>13</v>
       </c>
       <c r="K120" s="14" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>18</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L127" s="11" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>37</v>
       </c>
       <c r="K140" s="14" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="L140" s="14" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>6817.2</v>
       </c>
       <c r="P153" s="18" t="n">
-        <v>46.19</v>
+        <v>43.06</v>
       </c>
     </row>
   </sheetData>
@@ -12551,7 +12551,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>93.25</v>
+        <v>101</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>15.25</v>
@@ -12560,7 +12560,7 @@
         <v>5.08</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>113.58</v>
+        <v>121.33</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>9.25</v>
@@ -12570,7 +12570,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>23.9%</t>
         </is>
       </c>
     </row>
@@ -12581,7 +12581,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>26.75</v>
+        <v>29.75</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -12590,7 +12590,7 @@
         <v>7.25</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -12600,7 +12600,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>15.8%</t>
         </is>
       </c>
     </row>
@@ -12700,13 +12700,13 @@
         <v>506795</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>223799</v>
+        <v>214701</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>282996</v>
+        <v>292094</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>220984</v>
+        <v>230082</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>16651</v>
@@ -12750,13 +12750,13 @@
         <v>243482</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>154738</v>
+        <v>145640</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>88744</v>
+        <v>97842</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>46056</v>
+        <v>55154</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>7476</v>
@@ -12776,13 +12776,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -12800,7 +12800,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 17 commande(s)</t>
+          <t>Épics créées ce mois — 18 commande(s)</t>
         </is>
       </c>
     </row>
@@ -13170,22 +13170,22 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36197</t>
+          <t>PDMDEP-36402</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36190</t>
+          <t>PDMDEP-36398</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BAUGE-EN-ANJOU</t>
+          <t>COMMUNAUTÉ DE COMMUNES DE VIE ET BOULOGNE</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -13195,7 +13195,7 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -13205,32 +13205,32 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>00183894</t>
+          <t>00184748</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
-        <v>5718</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36252</t>
+          <t>PDMDEP-36197</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36247</t>
+          <t>PDMDEP-36190</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D AVIGNON</t>
+          <t>COMMUNE DE BAUGE-EN-ANJOU</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -13250,17 +13250,17 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>tasks</t>
+          <t>00183894</t>
         </is>
       </c>
       <c r="I13" s="25" t="n">
-        <v>0</v>
+        <v>5718</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36253</t>
+          <t>PDMDEP-36252</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
@@ -13295,7 +13295,7 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>apps.sogelink.fr</t>
+          <t>tasks</t>
         </is>
       </c>
       <c r="I14" s="26" t="n">
@@ -13305,7 +13305,7 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36255</t>
+          <t>PDMDEP-36253</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>sogetask</t>
+          <t>apps.sogelink.fr</t>
         </is>
       </c>
       <c r="I15" s="25" t="n">
@@ -13395,7 +13395,7 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36257</t>
+          <t>PDMDEP-36255</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>infos</t>
+          <t>sogetask</t>
         </is>
       </c>
       <c r="I17" s="25" t="n">
@@ -13440,7 +13440,7 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36258</t>
+          <t>PDMDEP-36257</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>https:</t>
+          <t>infos</t>
         </is>
       </c>
       <c r="I18" s="26" t="n">
@@ -13485,7 +13485,7 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36259</t>
+          <t>PDMDEP-36258</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
@@ -13518,7 +13518,11 @@
           <t>Services</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr"/>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>https:</t>
+        </is>
+      </c>
       <c r="I19" s="25" t="n">
         <v>0</v>
       </c>
@@ -13526,7 +13530,7 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36254</t>
+          <t>PDMDEP-36259</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
@@ -13559,11 +13563,7 @@
           <t>Services</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
-        <is>
-          <t>1849345</t>
-        </is>
-      </c>
+      <c r="H20" s="11" t="inlineStr"/>
       <c r="I20" s="26" t="n">
         <v>0</v>
       </c>
@@ -13571,73 +13571,97 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-36254</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-36247</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE D AVIGNON</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>1849345</t>
+        </is>
+      </c>
+      <c r="I21" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-36148</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-36144</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>VILLE DE VILLEFRANCHE SUR SAONE</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>00183228</t>
         </is>
       </c>
-      <c r="I21" s="25" t="n">
+      <c r="I22" s="26" t="n">
         <v>2310</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
-      <c r="F22" s="17" t="n"/>
-      <c r="G22" s="17" t="n"/>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>17 commande(s)</t>
-        </is>
-      </c>
-      <c r="I22" s="24" t="n">
-        <v>13313</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B23" s="17" t="n"/>
@@ -13648,17 +13672,17 @@
       <c r="G23" s="17" t="n"/>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>10 commande(s)</t>
+          <t>18 commande(s)</t>
         </is>
       </c>
       <c r="I23" s="24" t="n">
-        <v>8028</v>
+        <v>13313</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B24" s="17" t="n"/>
@@ -13669,10 +13693,31 @@
       <c r="G24" s="17" t="n"/>
       <c r="H24" s="17" t="inlineStr">
         <is>
+          <t>11 commande(s)</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="n">
+        <v>8028</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
+      <c r="G25" s="17" t="n"/>
+      <c r="H25" s="17" t="inlineStr">
+        <is>
           <t>7 commande(s)</t>
         </is>
       </c>
-      <c r="I24" s="24" t="n">
+      <c r="I25" s="24" t="n">
         <v>5285</v>
       </c>
     </row>

--- a/jira_export_2026-10-14.xlsx
+++ b/jira_export_2026-10-14.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>6,817 €</t>
+          <t>7,864 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -767,7 +767,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>4,123 €</t>
+          <t>5,170 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>222 h</t>
+          <t>223 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>294</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -6402,10 +6402,10 @@
         </is>
       </c>
       <c r="N79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="12" t="n">
         <v>1047</v>
-      </c>
-      <c r="O79" s="16" t="n">
-        <v>0</v>
       </c>
       <c r="P79" s="12" t="n">
         <v>0</v>
@@ -10877,7 +10877,7 @@
         <v>37</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="L143" s="11" t="inlineStr">
         <is>
@@ -11418,13 +11418,13 @@
       <c r="L153" s="17" t="inlineStr"/>
       <c r="M153" s="17" t="inlineStr"/>
       <c r="N153" s="18" t="n">
-        <v>120920.717</v>
+        <v>119873.717</v>
       </c>
       <c r="O153" s="18" t="n">
-        <v>6817.2</v>
+        <v>7864.200000000001</v>
       </c>
       <c r="P153" s="18" t="n">
-        <v>43.06</v>
+        <v>49.44</v>
       </c>
     </row>
   </sheetData>
@@ -11589,12 +11589,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
@@ -11615,7 +11615,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tickets 'Matériel GEODP' clôturés ce mois — 7 ligne(s)</t>
+          <t>Tickets 'Matériel GEODP' clôturés ce mois — 8 ligne(s)</t>
         </is>
       </c>
     </row>
@@ -11945,22 +11945,22 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-33149</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration GeODP</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -11983,12 +11983,12 @@
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31819</t>
+          <t>PDMDEP-33156</t>
         </is>
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>00159472</t>
+          <t>00165721</t>
         </is>
       </c>
       <c r="K10" s="15" t="n">
@@ -11998,22 +11998,22 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -12036,12 +12036,12 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31486</t>
+          <t>PDMDEP-31819</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>00157474</t>
+          <t>00159472</t>
         </is>
       </c>
       <c r="K11" s="12" t="n">
@@ -12049,22 +12049,75 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-31479</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE TREGUIER</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Migration vers GeoDP V2</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-31486</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>00157474</t>
+        </is>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr"/>
-      <c r="C12" s="17" t="inlineStr"/>
-      <c r="D12" s="17" t="inlineStr"/>
-      <c r="E12" s="17" t="inlineStr"/>
-      <c r="F12" s="17" t="inlineStr"/>
-      <c r="G12" s="17" t="inlineStr"/>
-      <c r="H12" s="17" t="inlineStr"/>
-      <c r="I12" s="17" t="inlineStr"/>
-      <c r="J12" s="17" t="inlineStr"/>
-      <c r="K12" s="18" t="n">
-        <v>7335</v>
+      <c r="B13" s="17" t="inlineStr"/>
+      <c r="C13" s="17" t="inlineStr"/>
+      <c r="D13" s="17" t="inlineStr"/>
+      <c r="E13" s="17" t="inlineStr"/>
+      <c r="F13" s="17" t="inlineStr"/>
+      <c r="G13" s="17" t="inlineStr"/>
+      <c r="H13" s="17" t="inlineStr"/>
+      <c r="I13" s="17" t="inlineStr"/>
+      <c r="J13" s="17" t="inlineStr"/>
+      <c r="K13" s="18" t="n">
+        <v>8150</v>
       </c>
     </row>
   </sheetData>
@@ -12077,6 +12130,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12551,7 +12605,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>101</v>
+        <v>101.75</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>15.25</v>
@@ -12560,7 +12614,7 @@
         <v>5.08</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>121.33</v>
+        <v>122.08</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>9.25</v>
@@ -12570,7 +12624,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.0%</t>
         </is>
       </c>
     </row>
@@ -12697,16 +12751,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>506795</v>
+        <v>505748</v>
       </c>
       <c r="C5" s="24" t="n">
         <v>214701</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>292094</v>
+        <v>291047</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>230082</v>
+        <v>229035</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>16651</v>
@@ -12747,16 +12801,16 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>243482</v>
+        <v>242435</v>
       </c>
       <c r="C7" s="26" t="n">
         <v>145640</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>97842</v>
+        <v>96795</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>55154</v>
+        <v>54107</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>7476</v>
@@ -12776,7 +12830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12800,7 +12854,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 18 commande(s)</t>
+          <t>Épics créées ce mois — 19 commande(s)</t>
         </is>
       </c>
     </row>
@@ -13170,12 +13224,12 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36402</t>
+          <t>PDMDEP-36414</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36398</t>
+          <t>PDMDEP-36410</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -13185,7 +13239,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTÉ DE COMMUNES DE VIE ET BOULOGNE</t>
+          <t>COMMUNE DE LA CHAPELLE PALLUAU</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -13205,7 +13259,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>00184748</t>
+          <t>XXX</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
@@ -13571,22 +13625,22 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36254</t>
+          <t>PDMDEP-36402</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36247</t>
+          <t>PDMDEP-36398</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D AVIGNON</t>
+          <t>COMMUNAUTÉ DE COMMUNES DE VIE ET BOULOGNE</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
@@ -13596,7 +13650,7 @@
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -13606,7 +13660,7 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>1849345</t>
+          <t>00184748</t>
         </is>
       </c>
       <c r="I21" s="25" t="n">
@@ -13616,73 +13670,97 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-36254</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36247</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE D AVIGNON</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>1849345</t>
+        </is>
+      </c>
+      <c r="I22" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
           <t>PDMDEP-36148</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-36144</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>VILLE DE VILLEFRANCHE SUR SAONE</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>00183228</t>
         </is>
       </c>
-      <c r="I22" s="26" t="n">
+      <c r="I23" s="25" t="n">
         <v>2310</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="17" t="n"/>
-      <c r="F23" s="17" t="n"/>
-      <c r="G23" s="17" t="n"/>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>18 commande(s)</t>
-        </is>
-      </c>
-      <c r="I23" s="24" t="n">
-        <v>13313</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B24" s="17" t="n"/>
@@ -13693,17 +13771,17 @@
       <c r="G24" s="17" t="n"/>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>11 commande(s)</t>
+          <t>19 commande(s)</t>
         </is>
       </c>
       <c r="I24" s="24" t="n">
-        <v>8028</v>
+        <v>13313</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B25" s="17" t="n"/>
@@ -13714,10 +13792,31 @@
       <c r="G25" s="17" t="n"/>
       <c r="H25" s="17" t="inlineStr">
         <is>
+          <t>12 commande(s)</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="n">
+        <v>8028</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
+      <c r="G26" s="17" t="n"/>
+      <c r="H26" s="17" t="inlineStr">
+        <is>
           <t>7 commande(s)</t>
         </is>
       </c>
-      <c r="I25" s="24" t="n">
+      <c r="I26" s="24" t="n">
         <v>5285</v>
       </c>
     </row>

--- a/jira_export_2026-10-14.xlsx
+++ b/jira_export_2026-10-14.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>223 h</t>
+          <t>234 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>296</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P153"/>
+  <dimension ref="A1:P154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -2461,7 +2461,7 @@
         <v>1</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L24" s="14" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -4813,7 +4813,7 @@
         <v>4</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>12.75</v>
+        <v>13.75</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         <v>11</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>11</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>11</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>11</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>11</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>11</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>18</v>
       </c>
       <c r="K128" s="14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
@@ -10514,22 +10514,22 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-15041</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CD38</t>
         </is>
       </c>
       <c r="E138" s="14" t="n">
@@ -10552,14 +10552,14 @@
       </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="J138" s="14" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K138" s="14" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="L138" s="14" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -10576,12 +10576,12 @@
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -10609,19 +10609,19 @@
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J139" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K139" s="11" t="n">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="L139" s="11" t="inlineStr"/>
       <c r="M139" s="11" t="inlineStr"/>
@@ -10638,12 +10638,12 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E140" s="14" t="n">
@@ -10666,35 +10666,27 @@
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H140" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J140" s="14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K140" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L140" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M140" s="14" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L140" s="14" t="inlineStr"/>
+      <c r="M140" s="14" t="inlineStr"/>
       <c r="N140" s="15" t="n">
         <v>0</v>
       </c>
@@ -10708,22 +10700,22 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
@@ -10736,23 +10728,35 @@
       </c>
       <c r="G141" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H141" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H141" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J141" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L141" s="11" t="inlineStr"/>
-      <c r="M141" s="11" t="inlineStr"/>
+        <v>1.25</v>
+      </c>
+      <c r="L141" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M141" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N141" s="12" t="n">
         <v>0</v>
       </c>
@@ -10766,12 +10770,12 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr">
@@ -10781,7 +10785,7 @@
       </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E142" s="14" t="n">
@@ -10797,32 +10801,20 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H142" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H142" s="14" t="inlineStr"/>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J142" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K142" s="14" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="L142" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M142" s="14" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="L142" s="14" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
       <c r="N142" s="15" t="n">
         <v>0</v>
       </c>
@@ -10836,22 +10828,22 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E143" s="11" t="n">
@@ -10864,29 +10856,33 @@
       </c>
       <c r="G143" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H143" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H143" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J143" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>1.5</v>
+        <v>6.75</v>
       </c>
       <c r="L143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-25456</t>
+          <t>PDMDEP-34532</t>
         </is>
       </c>
       <c r="M143" s="11" t="inlineStr">
         <is>
-          <t>424152</t>
+          <t>412263</t>
         </is>
       </c>
       <c r="N143" s="12" t="n">
@@ -10902,24 +10898,26 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C144" s="14" t="inlineStr"/>
+          <t>[CD06] Littéralis expert</t>
+        </is>
+      </c>
+      <c r="C144" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E144" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+        </is>
+      </c>
+      <c r="E144" s="14" t="n">
+        <v/>
       </c>
       <c r="F144" s="14" t="inlineStr">
         <is>
@@ -10928,27 +10926,31 @@
       </c>
       <c r="G144" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H144" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H144" s="14" t="inlineStr"/>
       <c r="I144" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J144" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K144" s="14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L144" s="14" t="inlineStr"/>
-      <c r="M144" s="14" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L144" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-25456</t>
+        </is>
+      </c>
+      <c r="M144" s="14" t="inlineStr">
+        <is>
+          <t>424152</t>
+        </is>
+      </c>
       <c r="N144" s="15" t="n">
         <v>0</v>
       </c>
@@ -10962,21 +10964,25 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>PSC-1363</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr"/>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
-        </is>
-      </c>
-      <c r="E145" s="11" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F145" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -10984,20 +10990,24 @@
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H145" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H145" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I145" s="11" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J145" s="11" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
       <c r="L145" s="11" t="inlineStr"/>
       <c r="M145" s="11" t="inlineStr"/>
@@ -11014,18 +11024,18 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>PSC-1351</t>
+          <t>PSC-1363</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="C146" s="14" t="inlineStr"/>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="E146" s="14" t="inlineStr"/>
@@ -11042,11 +11052,11 @@
       <c r="H146" s="14" t="inlineStr"/>
       <c r="I146" s="14" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="J146" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K146" s="14" t="n">
         <v>0.25</v>
@@ -11066,18 +11076,18 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>PSC-1346</t>
+          <t>PSC-1351</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr"/>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr"/>
@@ -11094,7 +11104,7 @@
       <c r="H147" s="11" t="inlineStr"/>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="J147" s="11" t="n">
@@ -11118,18 +11128,18 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PSC-1346</t>
         </is>
       </c>
       <c r="B148" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="C148" s="14" t="inlineStr"/>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="E148" s="14" t="inlineStr"/>
@@ -11140,35 +11150,27 @@
       </c>
       <c r="G148" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H148" s="14" t="inlineStr"/>
       <c r="I148" s="14" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="J148" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L148" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M148" s="14" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L148" s="14" t="inlineStr"/>
+      <c r="M148" s="14" t="inlineStr"/>
       <c r="N148" s="15" t="n">
-        <v>450</v>
-      </c>
-      <c r="O148" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P148" s="15" t="n">
@@ -11178,18 +11180,18 @@
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr"/>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr"/>
@@ -11200,27 +11202,35 @@
       </c>
       <c r="G149" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr"/>
       <c r="I149" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J149" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K149" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L149" s="11" t="inlineStr"/>
-      <c r="M149" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L149" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M149" s="11" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
       <c r="N149" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O149" s="12" t="n">
+        <v>450</v>
+      </c>
+      <c r="O149" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P149" s="12" t="n">
@@ -11230,18 +11240,18 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B150" s="14" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C150" s="14" t="inlineStr"/>
       <c r="D150" s="14" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E150" s="14" t="inlineStr"/>
@@ -11258,14 +11268,14 @@
       <c r="H150" s="14" t="inlineStr"/>
       <c r="I150" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J150" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K150" s="14" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="L150" s="14" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -11282,18 +11292,18 @@
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr"/>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr"/>
@@ -11304,31 +11314,23 @@
       </c>
       <c r="G151" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H151" s="11" t="inlineStr"/>
       <c r="I151" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J151" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K151" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L151" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M151" s="11" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="L151" s="11" t="inlineStr"/>
+      <c r="M151" s="11" t="inlineStr"/>
       <c r="N151" s="12" t="n">
         <v>0</v>
       </c>
@@ -11342,18 +11344,18 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>PSC-1047</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B152" s="14" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C152" s="14" t="inlineStr"/>
       <c r="D152" s="14" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E152" s="14" t="inlineStr"/>
@@ -11370,61 +11372,121 @@
       <c r="H152" s="14" t="inlineStr"/>
       <c r="I152" s="14" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J152" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K152" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L152" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M152" s="14" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N152" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1047</t>
+        </is>
+      </c>
+      <c r="B153" s="11" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="C153" s="11" t="inlineStr"/>
+      <c r="D153" s="11" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E153" s="11" t="inlineStr"/>
+      <c r="F153" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G153" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H153" s="11" t="inlineStr"/>
+      <c r="I153" s="11" t="inlineStr">
+        <is>
           <t>04/11/2025</t>
         </is>
       </c>
-      <c r="J152" s="14" t="n">
+      <c r="J153" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="K152" s="14" t="n">
+      <c r="K153" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L152" s="14" t="inlineStr">
+      <c r="L153" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-26768</t>
         </is>
       </c>
-      <c r="M152" s="14" t="inlineStr">
+      <c r="M153" s="11" t="inlineStr">
         <is>
           <t>00141775</t>
         </is>
       </c>
-      <c r="N152" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O152" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P152" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="17" t="inlineStr">
+      <c r="N153" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B153" s="17" t="inlineStr"/>
-      <c r="C153" s="17" t="inlineStr"/>
-      <c r="D153" s="17" t="inlineStr"/>
-      <c r="E153" s="17" t="inlineStr"/>
-      <c r="F153" s="17" t="inlineStr"/>
-      <c r="G153" s="17" t="inlineStr"/>
-      <c r="H153" s="17" t="inlineStr"/>
-      <c r="I153" s="17" t="inlineStr"/>
-      <c r="J153" s="17" t="inlineStr"/>
-      <c r="K153" s="17" t="inlineStr"/>
-      <c r="L153" s="17" t="inlineStr"/>
-      <c r="M153" s="17" t="inlineStr"/>
-      <c r="N153" s="18" t="n">
+      <c r="B154" s="17" t="inlineStr"/>
+      <c r="C154" s="17" t="inlineStr"/>
+      <c r="D154" s="17" t="inlineStr"/>
+      <c r="E154" s="17" t="inlineStr"/>
+      <c r="F154" s="17" t="inlineStr"/>
+      <c r="G154" s="17" t="inlineStr"/>
+      <c r="H154" s="17" t="inlineStr"/>
+      <c r="I154" s="17" t="inlineStr"/>
+      <c r="J154" s="17" t="inlineStr"/>
+      <c r="K154" s="17" t="inlineStr"/>
+      <c r="L154" s="17" t="inlineStr"/>
+      <c r="M154" s="17" t="inlineStr"/>
+      <c r="N154" s="18" t="n">
         <v>119873.717</v>
       </c>
-      <c r="O153" s="18" t="n">
+      <c r="O154" s="18" t="n">
         <v>7864.200000000001</v>
       </c>
-      <c r="P153" s="18" t="n">
-        <v>49.44</v>
+      <c r="P154" s="18" t="n">
+        <v>47.93</v>
       </c>
     </row>
   </sheetData>
@@ -11578,6 +11640,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId149"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12605,26 +12668,26 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>101.75</v>
+        <v>104</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>15.25</v>
+        <v>17.5</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>5.08</v>
+        <v>5.58</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>122.08</v>
+        <v>127.08</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>9.25</v>
+        <v>11.25</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>508.2</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -12666,7 +12729,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>53.33</v>
+        <v>57.08</v>
       </c>
     </row>
   </sheetData>
@@ -12830,7 +12893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12854,7 +12917,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 19 commande(s)</t>
+          <t>Épics créées ce mois — 22 commande(s)</t>
         </is>
       </c>
     </row>
@@ -12909,22 +12972,22 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36387</t>
+          <t>PDMDEP-36214</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36381</t>
+          <t>PDMDEP-36205</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRIANCON</t>
+          <t>COMME DE FECAMP</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -12944,32 +13007,32 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00184667</t>
+          <t>00176659</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36376</t>
+          <t>PDMDEP-36236</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36370</t>
+          <t>PDMDEP-36230</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SALON DE PROVENCE</t>
+          <t>COMMUNE DE QUIBERON</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -12989,32 +13052,32 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00184665</t>
+          <t>00183980</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>0</v>
+        <v>985</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36349</t>
+          <t>PDMDEP-36387</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36345</t>
+          <t>PDMDEP-36381</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LEUCATE Service Achat</t>
+          <t>COMMUNE DE BRIANCON</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -13024,7 +13087,7 @@
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -13034,7 +13097,7 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>00184482</t>
+          <t>00184667</t>
         </is>
       </c>
       <c r="I7" s="25" t="n">
@@ -13044,22 +13107,22 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36335</t>
+          <t>PDMDEP-36376</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36327</t>
+          <t>PDMDEP-36370</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>VILLE D'AIGLE</t>
+          <t>COMMUNE DE SALON DE PROVENCE</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -13079,7 +13142,7 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>00184406</t>
+          <t>00184665</t>
         </is>
       </c>
       <c r="I8" s="26" t="n">
@@ -13089,22 +13152,22 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36214</t>
+          <t>PDMDEP-36349</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36205</t>
+          <t>PDMDEP-36345</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>COMME DE FECAMP</t>
+          <t>MAIRIE DE LEUCATE Service Achat</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -13114,7 +13177,7 @@
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -13124,32 +13187,32 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>00176659</t>
+          <t>00184482</t>
         </is>
       </c>
       <c r="I9" s="25" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36236</t>
+          <t>PDMDEP-36335</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36230</t>
+          <t>PDMDEP-36327</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIBERON</t>
+          <t>VILLE D'AIGLE</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -13169,11 +13232,11 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>00183980</t>
+          <t>00184406</t>
         </is>
       </c>
       <c r="I10" s="26" t="n">
-        <v>985</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -13224,12 +13287,12 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36414</t>
+          <t>PDMDEP-36439</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36410</t>
+          <t>PDMDEP-36435</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -13239,7 +13302,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA CHAPELLE PALLUAU</t>
+          <t>COMMUNE D'ANGERS</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -13259,7 +13322,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>XXX</t>
+          <t>00184863</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
@@ -13404,7 +13467,7 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36256</t>
+          <t>PDMDEP-36254</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
@@ -13439,7 +13502,7 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>1849345</t>
         </is>
       </c>
       <c r="I16" s="26" t="n">
@@ -13494,7 +13557,7 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36257</t>
+          <t>PDMDEP-36258</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
@@ -13529,7 +13592,7 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>infos</t>
+          <t>https:</t>
         </is>
       </c>
       <c r="I18" s="26" t="n">
@@ -13539,7 +13602,7 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36258</t>
+          <t>PDMDEP-36257</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
@@ -13574,7 +13637,7 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>https:</t>
+          <t>infos</t>
         </is>
       </c>
       <c r="I19" s="25" t="n">
@@ -13670,22 +13733,22 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36254</t>
+          <t>PDMDEP-36414</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36247</t>
+          <t>PDMDEP-36410</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D AVIGNON</t>
+          <t>COMMUNE DE LA CHAPELLE PALLUAU</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -13695,7 +13758,7 @@
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
@@ -13705,7 +13768,7 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>1849345</t>
+          <t>XXX</t>
         </is>
       </c>
       <c r="I22" s="26" t="n">
@@ -13715,108 +13778,243 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-36427</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-36421</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>00184846</t>
+        </is>
+      </c>
+      <c r="I23" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36428</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36421</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>00184334</t>
+        </is>
+      </c>
+      <c r="I24" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-36256</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-36247</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE D AVIGNON</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="I25" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-36148</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-36144</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>VILLE DE VILLEFRANCHE SUR SAONE</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>00183228</t>
         </is>
       </c>
-      <c r="I23" s="25" t="n">
+      <c r="I26" s="26" t="n">
         <v>2310</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
-      <c r="F24" s="17" t="n"/>
-      <c r="G24" s="17" t="n"/>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>19 commande(s)</t>
-        </is>
-      </c>
-      <c r="I24" s="24" t="n">
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="17" t="n"/>
+      <c r="G27" s="17" t="n"/>
+      <c r="H27" s="17" t="inlineStr">
+        <is>
+          <t>22 commande(s)</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="n">
         <v>13313</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>dont Littéralis</t>
         </is>
       </c>
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="17" t="n"/>
-      <c r="F25" s="17" t="n"/>
-      <c r="G25" s="17" t="n"/>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>12 commande(s)</t>
-        </is>
-      </c>
-      <c r="I25" s="24" t="n">
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
+      <c r="G28" s="17" t="n"/>
+      <c r="H28" s="17" t="inlineStr">
+        <is>
+          <t>15 commande(s)</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="n">
         <v>8028</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>dont GEODP</t>
         </is>
       </c>
-      <c r="B26" s="17" t="n"/>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="17" t="n"/>
-      <c r="F26" s="17" t="n"/>
-      <c r="G26" s="17" t="n"/>
-      <c r="H26" s="17" t="inlineStr">
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="17" t="inlineStr">
         <is>
           <t>7 commande(s)</t>
         </is>
       </c>
-      <c r="I26" s="24" t="n">
+      <c r="I29" s="24" t="n">
         <v>5285</v>
       </c>
     </row>
